--- a/output/roomself_excel/11894.xlsx
+++ b/output/roomself_excel/11894.xlsx
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>200697</v>
+        <v>213957</v>
       </c>
       <c r="D2" t="n">
-        <v>3608</v>
+        <v>3992</v>
       </c>
       <c r="E2" t="n">
-        <v>530</v>
+        <v>342</v>
       </c>
       <c r="F2" t="n">
-        <v>453</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
@@ -488,17 +488,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>23166</v>
+        <v>42212</v>
       </c>
       <c r="D3" t="n">
-        <v>1220</v>
+        <v>1668</v>
       </c>
       <c r="E3" t="n">
-        <v>162</v>
+        <v>244</v>
       </c>
       <c r="F3" t="n">
         <v>27</v>
@@ -510,17 +510,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>90980</v>
+        <v>238760</v>
       </c>
       <c r="D4" t="n">
-        <v>2732</v>
+        <v>3912</v>
       </c>
       <c r="E4" t="n">
-        <v>213</v>
+        <v>508</v>
       </c>
       <c r="F4" t="n">
         <v>27</v>
@@ -536,13 +536,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>132540</v>
+        <v>90980</v>
       </c>
       <c r="D5" t="n">
-        <v>3008</v>
+        <v>2732</v>
       </c>
       <c r="E5" t="n">
-        <v>282</v>
+        <v>213</v>
       </c>
       <c r="F5" t="n">
         <v>27</v>
@@ -554,17 +554,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>238760</v>
+        <v>132540</v>
       </c>
       <c r="D6" t="n">
-        <v>3912</v>
+        <v>3008</v>
       </c>
       <c r="E6" t="n">
-        <v>508</v>
+        <v>282</v>
       </c>
       <c r="F6" t="n">
         <v>27</v>
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>43912</v>
+        <v>131950</v>
       </c>
       <c r="D7" t="n">
-        <v>1912</v>
+        <v>2908</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>33043</v>
+        <v>13462</v>
       </c>
       <c r="D8" t="n">
-        <v>1456</v>
+        <v>932</v>
       </c>
       <c r="E8" t="n">
-        <v>357</v>
+        <v>127</v>
       </c>
       <c r="F8" t="n">
-        <v>191</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5487</v>
+        <v>34827</v>
       </c>
       <c r="D9" t="n">
-        <v>608</v>
+        <v>1552</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>213957</v>
+        <v>33043</v>
       </c>
       <c r="D10" t="n">
-        <v>3992</v>
+        <v>1456</v>
       </c>
       <c r="E10" t="n">
-        <v>763</v>
+        <v>176</v>
       </c>
       <c r="F10" t="n">
-        <v>283</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11">
@@ -686,17 +686,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>131950</v>
+        <v>14522</v>
       </c>
       <c r="D12" t="n">
-        <v>2908</v>
+        <v>972</v>
       </c>
       <c r="E12" t="n">
-        <v>350</v>
+        <v>137</v>
       </c>
       <c r="F12" t="n">
         <v>27</v>
@@ -708,20 +708,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>42212</v>
+        <v>43912</v>
       </c>
       <c r="D13" t="n">
-        <v>1668</v>
+        <v>1912</v>
       </c>
       <c r="E13" t="n">
-        <v>244</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -730,20 +730,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>14522</v>
+        <v>200697</v>
       </c>
       <c r="D14" t="n">
-        <v>972</v>
+        <v>3608</v>
       </c>
       <c r="E14" t="n">
-        <v>137</v>
+        <v>530</v>
       </c>
       <c r="F14" t="n">
-        <v>27</v>
+        <v>453</v>
       </c>
     </row>
     <row r="15">
@@ -752,17 +752,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>13462</v>
+        <v>23166</v>
       </c>
       <c r="D15" t="n">
-        <v>932</v>
+        <v>1220</v>
       </c>
       <c r="E15" t="n">
-        <v>127</v>
+        <v>162</v>
       </c>
       <c r="F15" t="n">
         <v>27</v>
@@ -778,16 +778,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>161480</v>
+        <v>5487</v>
       </c>
       <c r="D16" t="n">
-        <v>3228</v>
+        <v>608</v>
       </c>
       <c r="E16" t="n">
-        <v>440</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -800,16 +800,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>40903</v>
+        <v>161480</v>
       </c>
       <c r="D17" t="n">
-        <v>1724</v>
+        <v>3228</v>
       </c>
       <c r="E17" t="n">
-        <v>216</v>
+        <v>440</v>
       </c>
       <c r="F17" t="n">
-        <v>27</v>
+        <v>421</v>
       </c>
     </row>
     <row r="18">
@@ -818,14 +818,14 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>34827</v>
+        <v>40903</v>
       </c>
       <c r="D18" t="n">
-        <v>1552</v>
+        <v>1724</v>
       </c>
       <c r="E18" t="n">
         <v>216</v>

--- a/output/roomself_excel/11894.xlsx
+++ b/output/roomself_excel/11894.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,12 +495,20 @@
       <c r="D2" t="n">
         <v>3992</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>342</v>
       </c>
-      <c r="F2" t="n">
-        <v>27</v>
-      </c>
+      <c r="G2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +525,20 @@
       <c r="D3" t="n">
         <v>1668</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>244</v>
       </c>
-      <c r="F3" t="n">
-        <v>27</v>
-      </c>
+      <c r="G3" t="n">
+        <v>27</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,11 +555,27 @@
       <c r="D4" t="n">
         <v>3912</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>508</v>
       </c>
-      <c r="F4" t="n">
-        <v>27</v>
+      <c r="G4" t="n">
+        <v>27</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>470</v>
+      </c>
+      <c r="J4" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="5">
@@ -541,12 +593,20 @@
       <c r="D5" t="n">
         <v>2732</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>213</v>
       </c>
-      <c r="F5" t="n">
-        <v>27</v>
-      </c>
+      <c r="G5" t="n">
+        <v>27</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +623,20 @@
       <c r="D6" t="n">
         <v>3008</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>282</v>
       </c>
-      <c r="F6" t="n">
-        <v>27</v>
-      </c>
+      <c r="G6" t="n">
+        <v>27</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,10 +653,26 @@
       <c r="D7" t="n">
         <v>2908</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>377</v>
+      </c>
+      <c r="G7" t="n">
+        <v>26</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>350</v>
       </c>
-      <c r="F7" t="n">
+      <c r="J7" t="n">
         <v>27</v>
       </c>
     </row>
@@ -607,12 +691,20 @@
       <c r="D8" t="n">
         <v>932</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>127</v>
       </c>
-      <c r="F8" t="n">
-        <v>27</v>
-      </c>
+      <c r="G8" t="n">
+        <v>27</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,11 +721,27 @@
       <c r="D9" t="n">
         <v>1552</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>216</v>
       </c>
-      <c r="F9" t="n">
-        <v>27</v>
+      <c r="G9" t="n">
+        <v>27</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>172</v>
+      </c>
+      <c r="J9" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="10">
@@ -651,12 +759,20 @@
       <c r="D10" t="n">
         <v>1456</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>176</v>
       </c>
-      <c r="F10" t="n">
-        <v>27</v>
-      </c>
+      <c r="G10" t="n">
+        <v>27</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +789,12 @@
       <c r="D11" t="n">
         <v>2140</v>
       </c>
-      <c r="E11" t="n">
-        <v>144</v>
-      </c>
-      <c r="F11" t="n">
-        <v>11</v>
-      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +811,20 @@
       <c r="D12" t="n">
         <v>972</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>137</v>
       </c>
-      <c r="F12" t="n">
-        <v>27</v>
-      </c>
+      <c r="G12" t="n">
+        <v>27</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +841,12 @@
       <c r="D13" t="n">
         <v>1912</v>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,11 +863,27 @@
       <c r="D14" t="n">
         <v>3608</v>
       </c>
-      <c r="E14" t="n">
-        <v>530</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F14" t="n">
-        <v>453</v>
+        <v>806</v>
+      </c>
+      <c r="G14" t="n">
+        <v>27</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>399</v>
+      </c>
+      <c r="J14" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -761,12 +901,20 @@
       <c r="D15" t="n">
         <v>1220</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
         <v>162</v>
       </c>
-      <c r="F15" t="n">
-        <v>27</v>
-      </c>
+      <c r="G15" t="n">
+        <v>27</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +931,12 @@
       <c r="D16" t="n">
         <v>608</v>
       </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,12 +953,20 @@
       <c r="D17" t="n">
         <v>3228</v>
       </c>
-      <c r="E17" t="n">
-        <v>440</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F17" t="n">
-        <v>421</v>
-      </c>
+        <v>865</v>
+      </c>
+      <c r="G17" t="n">
+        <v>27</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -827,11 +983,27 @@
       <c r="D18" t="n">
         <v>1724</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
         <v>216</v>
       </c>
-      <c r="F18" t="n">
-        <v>27</v>
+      <c r="G18" t="n">
+        <v>27</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>184</v>
+      </c>
+      <c r="J18" t="n">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
